--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-documentreference.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-documentreference.xlsx
@@ -458,7 +458,7 @@
     <t>DocumentReference.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -496,7 +496,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -554,7 +554,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -790,7 +790,7 @@
     <t>正確なタイプの臨床文書。 / Precise type of clinical document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-doc-typecodes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-doc-typecodes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -837,7 +837,7 @@
     <t>マクロレベルでの高レベルの臨床文書。 / High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
   </si>
   <si>
     <t>Composition.class</t>
@@ -855,7 +855,7 @@
     <t>DocumentReference.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|Group|Device)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|Group|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -917,7 +917,7 @@
     <t>DocumentReference.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|Device|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -951,7 +951,7 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -985,7 +985,7 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1092,7 +1092,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1236,7 +1236,7 @@
     <t>ドキュメント形式コード。 / Document Format Codes.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/formatcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/formatcodes|4.0.1</t>
   </si>
   <si>
     <t>Composition.meta.profile</t>
@@ -1275,7 +1275,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1365,7 +1365,7 @@
     <t>XDS施設タイプ。 / XDS Facility Type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-facilitycodes|4.0.1</t>
   </si>
   <si>
     <t>usually from a mapping to a local ValueSet</t>
@@ -1398,7 +1398,7 @@
     <t>コンテンツが作成された場所に関する追加の詳細（臨床専門分野など）。 / Additional details about where the content was created (e.g. clinical specialty).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>DocumentEntry.practiceSettingCode</t>
@@ -1407,7 +1407,7 @@
     <t>DocumentReference.context.sourcePatientInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1423,7 +1423,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1775,7 +1775,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.81640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
